--- a/examples/portfolio.xlsx
+++ b/examples/portfolio.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,16 +32,52 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,11 +85,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -62,6 +112,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -136,6 +195,151 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The program. One row per funding option; the first row carries Category, Mandatory and Requires.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. A grouping for the results.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. yes to always fund it.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Candidates it depends on, separated by ;.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The funding option: Full, Reduced rate, Defer...</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The benefit score of funding it this way.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. That year's cost for this option.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. That year's cost for this option.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. That year's cost for this option.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. That year's cost for this option.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. That year's cost for this option.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The fiscal year.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The money available that year.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Candidates only one of which may be funded, separated by ;.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>What the costs and budget are in.</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>The extra money to test in one year.</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>Cost growth factor, low: 0.92 means 8% under.</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>Cost growth factor, most likely: 1.0.</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>Cost growth factor, high: 1.45 means 45% over.</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>How much programs' growth moves together, 0 to 1.</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>Any whole number.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -424,10 +628,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -444,428 +649,760 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Requires</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" s="5" t="n">
         <v>2027</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" s="5" t="n">
         <v>2028</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" s="5" t="n">
         <v>2029</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" s="5" t="n">
         <v>2030</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" s="5" t="n">
         <v>2031</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Fleet sustainment</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Readiness</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="6" t="n">
         <v>420</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="6" t="n">
         <v>430</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="6" t="n">
         <v>440</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="6" t="n">
         <v>450</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="6" t="n">
         <v>460</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Munitions buy</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Readiness</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Full rate</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="6" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Munitions buy</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Minimum sustaining rate</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="6" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Sensor: upgrade in place</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Modernization</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Fund</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="6" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Sensor: new development</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Modernization</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Start now</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="6" t="n">
         <v>260</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="6" t="n">
         <v>280</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="6" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Sensor: new development</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Defer two years</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="6" t="n">
         <v>260</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="6" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Long-range missile</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Modernization</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="6" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Missile integration</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Modernization</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Long-range missile</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="6" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Training ranges</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="6" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Cyber hardening</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="6" t="n">
         <v>60</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C36" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="stop">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -873,96 +1410,275 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="6" t="n">
         <v>2027</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="6" t="n">
         <v>2028</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>1050</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="6" t="n">
         <v>2029</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="6" t="n">
         <v>2030</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="6" t="n">
         <v>2031</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>1100</v>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Candidates</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Sensor: upgrade in place; Sensor: new development</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -974,96 +1690,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>TY $M</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Growth Low</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>0.92</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Growth Most Likely</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Growth High</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>1.45</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Growth Correlation</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Invented programs and numbers, for illustration only. Then-year $M, a five-year plan.</t>
         </is>
@@ -1071,16 +1787,18 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1088,74 +1806,141 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>How to fill in this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Yellow cells</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Yours to fill in. The example rows are there to show the layout: type over them, and add more rows in the yellow space below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Dark blue heading</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>A column that must be filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Light blue heading</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>An optional column: leave it blank if it doesn't apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Grey cells</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Labels: leave them as they are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Hover over a heading</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>A note says what goes in that column, in what units, with an example. A small arrow in a cell means a drop-down list of the allowed answers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Sheet or topic</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>What to put there</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>What this is</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Candidate programs, their funding options and the budget, for choosing what to fund: ce-core portfolio --spec &lt;this file&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Candidates sheet</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>One row per funding option. A candidate with several options (full rate, minimum rate, defer) takes one row each; at most one is funded. Value is the benefit score. The year columns hold the cost in each year. Category, Mandatory (yes to always fund it) and Requires (candidates it depends on, separated by ;) go on its first row.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Budget sheet</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>The money available in each year.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Exclusive sheet</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Candidates only one of which may be funded, separated by ; on a row.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Settings sheet</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Growth Low, Most Likely and High are the cost growth factors for the risk analysis (0.92, 1.0, 1.45). Delta is the budget step for the trade-off curve.</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Growth Low, Most Likely and High are the cost growth factors for the risk analysis (0.92, 1.0, 1.45). Delta is the extra money to test in one year: what it would buy if added to each year in turn. Frontier Scales are the budget levels for the trade-off curve (0.9; 1.0; 1.1).</t>
         </is>
       </c>
     </row>
